--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.40623742301265</v>
+        <v>7.541013581239556</v>
       </c>
       <c r="D2" t="n">
-        <v>44.61818902993551</v>
+        <v>7.250455717364521</v>
       </c>
       <c r="E2" t="n">
-        <v>18.50838744947697</v>
+        <v>3.007612960540008</v>
       </c>
       <c r="F2" t="n">
-        <v>17.91079608178801</v>
+        <v>2.910504363290552</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>74.98854448643337</v>
+        <v>12.18563847904542</v>
       </c>
       <c r="D3" t="n">
-        <v>73.6066287260866</v>
+        <v>11.96107716798907</v>
       </c>
       <c r="E3" t="n">
-        <v>18.50838744947697</v>
+        <v>3.007612960540008</v>
       </c>
       <c r="F3" t="n">
-        <v>17.91079608178801</v>
+        <v>2.910504363290552</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.58906561213464</v>
+        <v>8.220723161971879</v>
       </c>
       <c r="D4" t="n">
-        <v>49.13255198294945</v>
+        <v>7.984039697229286</v>
       </c>
       <c r="E4" t="n">
-        <v>18.50838744947697</v>
+        <v>3.007612960540008</v>
       </c>
       <c r="F4" t="n">
-        <v>17.91079608178801</v>
+        <v>2.910504363290552</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.40206434758852</v>
+        <v>5.590335456483134</v>
       </c>
       <c r="D5" t="n">
-        <v>33.81570350339797</v>
+        <v>5.49505181930217</v>
       </c>
       <c r="E5" t="n">
-        <v>18.50838744947697</v>
+        <v>3.007612960540008</v>
       </c>
       <c r="F5" t="n">
-        <v>17.91079608178801</v>
+        <v>2.910504363290552</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.47115770694409</v>
+        <v>5.926563127378415</v>
       </c>
       <c r="D6" t="n">
-        <v>35.92770733460441</v>
+        <v>5.838252441873218</v>
       </c>
       <c r="E6" t="n">
-        <v>18.50838744947697</v>
+        <v>3.007612960540008</v>
       </c>
       <c r="F6" t="n">
-        <v>17.91079608178801</v>
+        <v>2.910504363290552</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.81906760005284</v>
+        <v>6.145598485008587</v>
       </c>
       <c r="D7" t="n">
-        <v>37.5423942766306</v>
+        <v>6.100639069952472</v>
       </c>
       <c r="E7" t="n">
-        <v>18.50838744947697</v>
+        <v>3.007612960540008</v>
       </c>
       <c r="F7" t="n">
-        <v>17.91079608178801</v>
+        <v>2.910504363290552</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>10.51072794834075</v>
+        <v>1.707993291605372</v>
       </c>
       <c r="D8" t="n">
-        <v>11.12169055628026</v>
+        <v>1.807274715395543</v>
       </c>
       <c r="E8" t="n">
-        <v>18.50838744947697</v>
+        <v>3.007612960540008</v>
       </c>
       <c r="F8" t="n">
-        <v>17.91079608178801</v>
+        <v>2.910504363290552</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>14.53086586467797</v>
+        <v>2.36126570301017</v>
       </c>
       <c r="D9" t="n">
-        <v>14.36149017097152</v>
+        <v>2.333742152782873</v>
       </c>
       <c r="E9" t="n">
-        <v>18.50838744947697</v>
+        <v>3.007612960540008</v>
       </c>
       <c r="F9" t="n">
-        <v>17.91079608178801</v>
+        <v>2.910504363290552</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>14.42498503313374</v>
+        <v>2.344060067884233</v>
       </c>
       <c r="D10" t="n">
-        <v>14.55294131936585</v>
+        <v>2.36485296439695</v>
       </c>
       <c r="E10" t="n">
-        <v>18.50838744947697</v>
+        <v>3.007612960540008</v>
       </c>
       <c r="F10" t="n">
-        <v>17.91079608178801</v>
+        <v>2.910504363290552</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.50914549174761</v>
+        <v>5.445236142408987</v>
       </c>
       <c r="D11" t="n">
-        <v>33.35319110797296</v>
+        <v>5.419893555045606</v>
       </c>
       <c r="E11" t="n">
-        <v>18.50838744947697</v>
+        <v>3.007612960540008</v>
       </c>
       <c r="F11" t="n">
-        <v>17.91079608178801</v>
+        <v>2.910504363290552</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
